--- a/pre-processing/data_cleaned/tv.xlsx
+++ b/pre-processing/data_cleaned/tv.xlsx
@@ -37,18 +37,21 @@
     <t>Smart Tivi LG AI 4K 55 Inch 55UA8450PSA- Hàng Chính Hãng</t>
   </si>
   <si>
-    <t>Smart Tivi LG AI 4K 65 Inch 65UA8450PSA- Hàng Chính Hãng</t>
-  </si>
-  <si>
     <t>Google Tivi Xiaomi A 2026 4K 55 inch L55MB-ASEA - Hàng chính hãng</t>
   </si>
   <si>
     <t>Google Tivi Xiaomi A 2026 4K 43 inch L43MB-AUSEA - Hàng chính hãng</t>
   </si>
   <si>
+    <t>Google Tivi Coocaa Full. HD 43 inch  43Z73 - hàng chính hãng</t>
+  </si>
+  <si>
     <t>Smart Tivi QLED Samsung 4K 55 inch QA55QE1DAKXXV - Hàng Chính Hãng</t>
   </si>
   <si>
+    <t>[NEW 2026 TV Series] Smart Tivi Xiaomi TV A 43 2026 - 43 Inch - UHD 4K - Hàng Chính Hãng</t>
+  </si>
+  <si>
     <t>Google Tivi TCL QLED Full HD 32 Inch 32S5K - Hàng chính hãng</t>
   </si>
   <si>
@@ -88,9 +91,6 @@
     <t>Smart Tivi Samsung 4K 65 Inch UA65DU7700 - HÀNG CHÍNH HÃNG - CHỈ GIAO HCM</t>
   </si>
   <si>
-    <t>Smart Tivi LG 4K 55 inch 55UT8050PSB - Hàng Chính Hãng</t>
-  </si>
-  <si>
     <t>Google Tivi Coocaa 4K 65 Inch 65Y73 - Hàng Chính Hãng - Chỉ Giao HCM</t>
   </si>
   <si>
@@ -112,523 +112,523 @@
     <t>Smart TV HD Coocaa 32 Inch Wifi - Model 32S3U+ - Hàng Chính Hãng</t>
   </si>
   <si>
+    <t>Ti vi smart COOCAA 43S3U-HÀNG CHÍNH HÃNG</t>
+  </si>
+  <si>
+    <t>Google Tivi Sony 4K 50 inch K-50S30 - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>QLED Tivi 4K Samsung 85Q60DA 85 inch Smart TV QA85Q60DA QA85Q60D 85Q60D - Hàng chính hãng - Chỉ giao HCM</t>
+  </si>
+  <si>
+    <t>Smart QLED Tivi 4K Samsung 55Q60DA 55 inch QA55Q60DA QA55Q60D 55Q60D - Hàng chính hãng - Chỉ giao HCM</t>
+  </si>
+  <si>
+    <t>Smart Tivi Samsung 4K 65 inch UA65DU8000 65DU8000 - Hàng chính hãng - Chỉ giao HCM</t>
+  </si>
+  <si>
+    <t>Smart Tivi Oled LG 55A3PSA 4K 55 Inch - HÀNG CHÍNH HÃNG ( CHỈ GIAO HCM )</t>
+  </si>
+  <si>
+    <t>Android TV K-Elec Full HD 43LK885V - Hàng nhập khẩu</t>
+  </si>
+  <si>
+    <t>Smart Tivi NanoCell LG 4K 55 Inch 55NANO76SQA [Hàng Chính Hãng]</t>
+  </si>
+  <si>
+    <t>Smart ti vi Asanzo 43 EH 7- hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Tivi TCL 4K 55 inch 55P638 - Hàng chính hãng (Chỉ giao HCM)</t>
+  </si>
+  <si>
+    <t>Smart Tivi Coocaa HD 32 inch 32S3U</t>
+  </si>
+  <si>
+    <t>Tivi LED Sharp HD 32 inch 2T-C32BD1X</t>
+  </si>
+  <si>
+    <t>Smart Tivi Asanzo Full HD 43 inch 43AS560</t>
+  </si>
+  <si>
+    <t>24P6300 - Google Tivi Xách Tay Di Động FHD 24 Inch Skyworth - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>TIVI LED SKYWORTH HD 32 INCH  32E5000G - HÀNG CHÍNH HÃNG - CHỈ GIAO HCM</t>
+  </si>
+  <si>
+    <t>Android Tivi LED Hisense 32 inch 32A4N trợ lý ảo Google Voice Control, bảo hành chính hãng 2 năm - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Smart Tivi Coocaa khung tranh QLED 4K 55 inch 55LN7000G - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Google Tivi Xiaomi QLED 4K 85 inch L85MA-MAXEA -  HÀNG CHÍNH HÃNG - CHỈ GIAO HCM</t>
+  </si>
+  <si>
+    <t>Smart tivi 65 inch Qled 4K tivi Khung Tranh Google Frame tivi coocaa 65LN7000G - HÀNG CHÍNH HÃNG - CHỈ GIAO HCM</t>
+  </si>
+  <si>
+    <t>Smart Tivi OLED LG 4K 55 inch 55G4PSA Mẫu mới - HÀNG CHÍNH HÃNG - CHỈ GIAO HCM</t>
+  </si>
+  <si>
+    <t>Android Tivi Aqua 43 inch AQT43K800UG - Hàng chính hãng - Bảo hành 1 đổi 1 trong 730 ngày đối với lỗi màn hình</t>
+  </si>
+  <si>
+    <t>Smart Tivi QLED TOSHIBA 55 inch 55M450NP, Màn Hình Quantum Dot 4K UHD -  Giao Hàng Toàn Quốc - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Skyworth Google TV 2K FHD 24P6300 - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Smart Tivi Skyworth 43E5000G 43 inch 43E5000G - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Smart Tivi NanoCell LG 4K 50 inch 50NANO81TSA - hàng chính hãng - chỉ giao tại HCM</t>
+  </si>
+  <si>
+    <t>K-85S30 - Google Tivi Sony 4K 85 inch K-85S30 - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>K-65XR70 - Google Tivi Mini LED Sony 4K 65 inch K-65XR70 - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Smart Tivi LG 4K 43 inch 43UT8050PSB Mới 2024 - Hàng chính hãng - Giao HCM và 1 số tỉnh thành</t>
+  </si>
+  <si>
+    <t>Smart Tivi NanoCell LG 4K 43 inch 43NANO81TSA Mới 2024 - Hàng chính hãng - Giao HCM và 1 số tỉnh thành</t>
+  </si>
+  <si>
+    <t>Smart Tivi OLED LG 4K 65 inch OLED65C4PSA Mới 2024 - Hàng chính hãng - Giao HCM và 1 số tỉnh thành</t>
+  </si>
+  <si>
+    <t>GOOGLE TI VI COOCAA 32Z73-HÀNG CHÍNH HÃNG- ĐIỀU KHIỂN GIỌNG NÓI</t>
+  </si>
+  <si>
+    <t>Google Tivi LED Sony 4K 43 inch K-43S30 VN3 - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Google Tivi Sony 4K 65 inch KD-65X75K - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Smart Tivi QLED 4K Samsung 43Q60DA 43 inch Smart TV QA43Q60DA QA43Q60D 43Q60D - Hàng chính hãng - Chỉ giao HCM</t>
+  </si>
+  <si>
+    <t>Smart Tivi Samsung 4K 85 inch UA85DU8000 85DU8000 - Hàng chính hãng - Chỉ giao HCM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Tivi Sony 4K 75 inch KD.75X77L - Hàng chính hãng </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smart Tivi LG 75UR7550PSC 4K 75 Inch - HÀNG CHÍNH HÃNG - CHỈ GIAO HCM </t>
+  </si>
+  <si>
+    <t>Android TV K-Elec 65UK885V - Hàng nhập khẩu</t>
+  </si>
+  <si>
+    <t>Android TV K-Elec HD 32LK885V - Hàng nhập khẩu</t>
+  </si>
+  <si>
+    <t>Tivi 32IN HÀNG CHÍNH HÃNG NHẬP KHẨU TỪ HÀN QUỐC</t>
+  </si>
+  <si>
+    <t>Google  ti vi Asanzo 32EX9- hàng chính hãng- ĐIỀU KHIỂN GIỌNG NÓI</t>
+  </si>
+  <si>
+    <t>Google Tivi Sony 32 inch KD-32W830K - Hàng chính hãng - Giao tại Hà Nội và 1 số tỉnh toàn quốc</t>
+  </si>
+  <si>
+    <t>Google Tivi TCL LED 4K 55 inch 55P638 - Hàng chính hãng( Chỉ giao tại HCM)</t>
+  </si>
+  <si>
+    <t>Google Tivi Coocaa 4K 55 Inch - Model 55Y72 - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Tivi Casper 43 inch 43FG5200 - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Google Tivi Mini LED Sony 4K 65 inch XR-65X95K - Model 2022</t>
+  </si>
+  <si>
+    <t>Google Tivi Sony 4K 43 inch KD-43X81DK - Model 2022</t>
+  </si>
+  <si>
+    <t>Google Tivi Sony 2K 32 inch KD-32W830K - Model 2022</t>
+  </si>
+  <si>
+    <t>ULED TIVI AKINO 55 inch TL-HU9 - android - Hàng Chính Hãng (Giao Hàng Toàn Quốc)</t>
+  </si>
+  <si>
+    <t>Android Tivi Aqua 4K 55 Inch LE55AQTS6UG - Hàng chính hãng (chỉ giao HCM)</t>
+  </si>
+  <si>
+    <t>Smart Tivi Casper HD 32 inch 32HX6200</t>
+  </si>
+  <si>
+    <t>Smart Tivi OLED LG 4K 65 inch OLED65GXPTA</t>
+  </si>
+  <si>
+    <t>Smart Tivi Cong QLED Samsung 4K 55 inch QA55Q8CNA</t>
+  </si>
+  <si>
+    <t>Google Tivi Hisense QLED Hisense 55 inch 55Q6N Google Assistant Có Tiếng Việt, Bảo Hành 3 Năm - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Android Tivi LED Hisense 43 inch A4N Trợ Lý Ảo Google Voice Control, Bảo Hành 2 Năm - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Android Tivi LED Hisense 40 inch A4N trợ lý ảo Google Voice Control, bảo hành 2 năm - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Smart Tivi OLED LG 4K 65 Inch 65M4PSA - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Smart Tivi Coocaa 65Y73 Pro 4K QLED 65 inch - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Android Tivi LED Hisense 43 inch 43A4N trợ lý ảo Google Voice Control, bảo hành 2 năm - HÀNG CHÍNH HÃNG</t>
+  </si>
+  <si>
+    <t>Google Tivi Aqua QLED 4K 50 inch AQT50S800UX - Freeship toàn quốc - Bảo hành 1 đổi 1 trong 730 ngày đối với lỗi màn hình - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>Google Tivi Aqua QLED 4K 50 inch AQT50S80EUX - Freeship toàn quốc - Bảo hành 1 đổi 1 trong 730 ngày đối với lỗi màn hình - Hàng chính hãng</t>
+  </si>
+  <si>
+    <t>K-65S30 - Google Tivi Sony 4K 65 inch K-65S30 - Hàng Chính Hãng - Chỉ Giao Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>K-75XR70 - Google Tivi Mini LED Sony 4K 75 inch K-75XR70 - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>K-65XR80 - Google Tivi OLED Sony 4K 65 inch K-65XR80 - Hàng Chính Hãng</t>
+  </si>
+  <si>
+    <t>Google Tivi Sony 4K 65 inch K-65S30 Mới 2024 - Hàng chính hãng - Giao HCM và 1 số tỉnh thành</t>
+  </si>
+  <si>
+    <t>Smart Tivi LG 4K 50 inch 50UT8050PSB Mới 2024 - Hàng chính hãng - Giao HCM và 1 số tỉnh thành</t>
+  </si>
+  <si>
+    <t>Smart Tivi NanoCell LG 4K 65 Inch 65NANO81TSA Mới 2024 - Hàng chính hãng - Giao HCM và 1 số tỉnh thành</t>
+  </si>
+  <si>
+    <t>Smart Tivi OLED LG 4K 65 inch OLED65B4PSA Mới 2024 - Hàng chính hãng - Giao HCM và 1 số tỉnh thành</t>
+  </si>
+  <si>
+    <t>Smart Tivi OLED LG 4K 55 inch OLED55C4PSA Mới 2024 - Hàng chính hãng - Giao HCM và 1 số tỉnh thành</t>
+  </si>
+  <si>
+    <t>Smart Tivi OLED LG 4K 77 inch OLED77C4PSA Mới 2024 - Hàng chính hãng - Giao HCM và 1 số tỉnh thành</t>
+  </si>
+  <si>
     <t>Google Tivi LED Sony 4K 55 inch K-55S30 VN3 - Hàng Chính Hãng</t>
   </si>
   <si>
-    <t>Google Tivi Sony 4K 50 inch K-50S30 - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>QLED Tivi 4K Samsung 85Q60DA 85 inch Smart TV QA85Q60DA QA85Q60D 85Q60D - Hàng chính hãng - Chỉ giao HCM</t>
-  </si>
-  <si>
-    <t>Smart QLED Tivi 4K Samsung 55Q60DA 55 inch QA55Q60DA QA55Q60D 55Q60D - Hàng chính hãng - Chỉ giao HCM</t>
-  </si>
-  <si>
-    <t>Smart Tivi Samsung 4K 65 inch UA65DU8000 65DU8000 - Hàng chính hãng - Chỉ giao HCM</t>
-  </si>
-  <si>
-    <t>Smart Tivi Oled LG 55A3PSA 4K 55 Inch - HÀNG CHÍNH HÃNG ( CHỈ GIAO HCM )</t>
-  </si>
-  <si>
-    <t>Android TV K-Elec Full HD 43LK885V - Hàng nhập khẩu</t>
-  </si>
-  <si>
-    <t>Smart Tivi NanoCell LG 4K 55 Inch 55NANO76SQA [Hàng Chính Hãng]</t>
-  </si>
-  <si>
-    <t>Tivi TCL 4K 55 inch 55P638 - Hàng chính hãng (Chỉ giao HCM)</t>
-  </si>
-  <si>
-    <t>Smart Tivi Coocaa HD 32 inch 32S3U</t>
-  </si>
-  <si>
-    <t>Smart Tivi Casper HD 32 inch 32HX6200</t>
-  </si>
-  <si>
-    <t>Tivi LED Sharp HD 32 inch 2T-C32BD1X</t>
-  </si>
-  <si>
-    <t>Smart Tivi Cong QLED Samsung 4K 55 inch QA55Q8CNA</t>
-  </si>
-  <si>
-    <t>[NEW 2026 TV Series] Smart Tivi Xiaomi TV A 43 2026 - 43 Inch - UHD 4K - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Smart Tivi Toshiba 65 inch 4K UHD 65E330NP, Giao Hàng Toàn Quốc - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>24P6300 - Google Tivi Xách Tay Di Động FHD 24 Inch Skyworth - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>TIVI LED SKYWORTH HD 32 INCH  32E5000G - HÀNG CHÍNH HÃNG - CHỈ GIAO HCM</t>
-  </si>
-  <si>
-    <t>Android Tivi LED Hisense 32 inch 32A4N trợ lý ảo Google Voice Control, bảo hành chính hãng 2 năm - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Smart Tivi Coocaa khung tranh QLED 4K 55 inch 55LN7000G - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Google Tivi Xiaomi QLED 4K 85 inch L85MA-MAXEA -  HÀNG CHÍNH HÃNG - CHỈ GIAO HCM</t>
-  </si>
-  <si>
-    <t>Smart Tivi OLED LG 4K 55 inch 55G4PSA Mẫu mới - HÀNG CHÍNH HÃNG - CHỈ GIAO HCM</t>
-  </si>
-  <si>
-    <t>Android Tivi Aqua 43 inch AQT43K800UG - Hàng chính hãng - Bảo hành 1 đổi 1 trong 730 ngày đối với lỗi màn hình</t>
-  </si>
-  <si>
-    <t>Smart Tivi QLED TOSHIBA 55 inch 55M450NP, Màn Hình Quantum Dot 4K UHD -  Giao Hàng Toàn Quốc - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Smart Tivi TOSHIBA 55 inch 55E330NP, Màn Hình LED 4K UHD - Giao Hàng Toàn Quốc - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Smart Tivi LG 4K 65 inch 65UT7350PSB - HÀNG CHÍNH HÃNG - CHỈ GIAO HCM</t>
-  </si>
-  <si>
-    <t>Skyworth Google TV 2K FHD 24P6300 - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Smart Tivi Skyworth 43E5000G 43 inch 43E5000G - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Smart Tivi NanoCell LG 4K 50 inch 50NANO81TSA - hàng chính hãng - chỉ giao tại HCM</t>
-  </si>
-  <si>
-    <t>K-85S30 - Google Tivi Sony 4K 85 inch K-85S30 - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>K-65XR70 - Google Tivi Mini LED Sony 4K 65 inch K-65XR70 - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Smart Tivi NanoCell LG 4K 55 Inch 55NANO81TSA Mới 2024 - Hàng chính hãng - Giao HCM và 1 số tỉnh thành</t>
-  </si>
-  <si>
-    <t>Smart Tivi LG 4K 43 inch 43UT8050PSB Mới 2024 - Hàng chính hãng - Giao HCM và 1 số tỉnh thành</t>
-  </si>
-  <si>
-    <t>Smart Tivi NanoCell LG 4K 43 inch 43NANO81TSA Mới 2024 - Hàng chính hãng - Giao HCM và 1 số tỉnh thành</t>
-  </si>
-  <si>
-    <t>Smart Tivi OLED LG 4K 65 inch OLED65C4PSA Mới 2024 - Hàng chính hãng - Giao HCM và 1 số tỉnh thành</t>
-  </si>
-  <si>
-    <t>Google Tivi LED Sony 4K 43 inch K-43S30 VN3 - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Google Tivi Sony 4K 65 inch KD-65X75K - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Smart QLED Tivi 4K Samsung 75Q60DA 75 inch QA75Q60DA QA75Q60D 75Q60D - Hàng chính hãng - Chỉ giao HCM</t>
-  </si>
-  <si>
-    <t>Smart Tivi QLED 4K Samsung 43Q60DA 43 inch Smart TV QA43Q60DA QA43Q60D 43Q60D - Hàng chính hãng - Chỉ giao HCM</t>
-  </si>
-  <si>
-    <t>Smart Tivi Samsung 4K 85 inch UA85DU8000 85DU8000 - Hàng chính hãng - Chỉ giao HCM</t>
-  </si>
-  <si>
-    <t>Smart Tivi Samsung 4K 55 inch UA55DU8000 55DU8000 - Hàng chính hãng - Chỉ giao HCM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google Tivi Sony 4K 75 inch KD.75X77L - Hàng chính hãng </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Smart Tivi LG 75UR7550PSC 4K 75 Inch - HÀNG CHÍNH HÃNG - CHỈ GIAO HCM </t>
-  </si>
-  <si>
-    <t>Android TV K-Elec HD 32LK885V - Hàng nhập khẩu</t>
-  </si>
-  <si>
-    <t>Tivi 32IN HÀNG CHÍNH HÃNG NHẬP KHẨU TỪ HÀN QUỐC</t>
-  </si>
-  <si>
-    <t>Google Tivi TCL LED 4K 55 inch 55P638 - Hàng chính hãng( Chỉ giao tại HCM)</t>
-  </si>
-  <si>
-    <t>Google Tivi Coocaa 4K 55 Inch - Model 55Y72 - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Tivi Casper 43 inch 43FG5200 - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Google Tivi Mini LED Sony 4K 65 inch XR-65X95K - Model 2022</t>
-  </si>
-  <si>
-    <t>Google Tivi Sony 4K 43 inch KD-43X81DK - Model 2022</t>
-  </si>
-  <si>
-    <t>Google Tivi Sony 2K 32 inch KD-32W830K - Model 2022</t>
-  </si>
-  <si>
-    <t>ULED TIVI AKINO 55 inch TL-HU9 - android - Hàng Chính Hãng (Giao Hàng Toàn Quốc)</t>
-  </si>
-  <si>
-    <t>Android Tivi Aqua 4K 55 Inch LE55AQTS6UG - Hàng chính hãng (chỉ giao HCM)</t>
-  </si>
-  <si>
-    <t>Smart Tivi OLED LG 4K 65 inch OLED65GXPTA</t>
-  </si>
-  <si>
-    <t>Smart Tivi Toshiba 55 inch 4K UHD 55E330NP, Giao Hàng Toàn Quốc - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Google Tivi Hisense QLED Hisense 55 inch 55Q6N Google Assistant Có Tiếng Việt, Bảo Hành 3 Năm - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Android Tivi LED Hisense 43 inch A4N Trợ Lý Ảo Google Voice Control, Bảo Hành 2 Năm - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Android Tivi LED Hisense 40 inch A4N trợ lý ảo Google Voice Control, bảo hành 2 năm - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Smart Tivi OLED LG 4K 65 Inch 65M4PSA - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Smart tivi 65 inch Qled 4K tivi Khung Tranh Google Frame tivi coocaa 65LN7000G - HÀNG CHÍNH HÃNG - CHỈ GIAO HCM</t>
-  </si>
-  <si>
-    <t>Android Tivi LED Hisense 43 inch 43A4N trợ lý ảo Google Voice Control, bảo hành 2 năm - HÀNG CHÍNH HÃNG</t>
-  </si>
-  <si>
-    <t>Google Tivi Aqua QLED 4K 50 inch AQT50S800UX - Freeship toàn quốc - Bảo hành 1 đổi 1 trong 730 ngày đối với lỗi màn hình - Hàng chính hãng</t>
-  </si>
-  <si>
-    <t>Smart Tivi NanoCell LG 4K 75 inch 75NANO81TSA - hàng chính hãng - chỉ giao tại HCM</t>
-  </si>
-  <si>
-    <t>K-65S30 - Google Tivi Sony 4K 65 inch K-65S30 - Hàng Chính Hãng - Chỉ Giao Hồ Chí Minh</t>
-  </si>
-  <si>
-    <t>UA55DU8000 - Smart Tivi Samsung 4K 55 inch UA55DU8000 - Hàng Chính Hãng - Chỉ Giao Hồ Chí Minh</t>
-  </si>
-  <si>
-    <t>K-75XR70 - Google Tivi Mini LED Sony 4K 75 inch K-75XR70 - Hàng Chính Hãng</t>
-  </si>
-  <si>
-    <t>Google Tivi Sony 4K 65 inch K-65S30 Mới 2024 - Hàng chính hãng - Giao HCM và 1 số tỉnh thành</t>
-  </si>
-  <si>
-    <t>Smart Tivi LG 4K 50 inch 50UT8050PSB Mới 2024 - Hàng chính hãng - Giao HCM và 1 số tỉnh thành</t>
-  </si>
-  <si>
-    <t>Smart Tivi NanoCell LG 4K 65 Inch 65NANO81TSA Mới 2024 - Hàng chính hãng - Giao HCM và 1 số tỉnh thành</t>
-  </si>
-  <si>
-    <t>Smart Tivi OLED LG 4K 65 inch OLED65B4PSA Mới 2024 - Hàng chính hãng - Giao HCM và 1 số tỉnh thành</t>
-  </si>
-  <si>
-    <t>Smart Tivi OLED LG 4K 55 inch OLED55C4PSA Mới 2024 - Hàng chính hãng - Giao HCM và 1 số tỉnh thành</t>
-  </si>
-  <si>
-    <t>Smart Tivi OLED LG 4K 77 inch OLED77C4PSA Mới 2024 - Hàng chính hãng - Giao HCM và 1 số tỉnh thành</t>
+    <t>GOOGLE TI VI 43 ASANZO-43EX9- ĐIỀU KHIẾU GIỌNG NÓI- HÀNG CHÍNH HÃNG</t>
   </si>
   <si>
     <t>Smart Tivi Samsung Neo QLED 8K 65 Inch QA65QN800D QA65QN800DA 65QN800DA 65QN800D - Hàng chính hãng - Chỉ giao HCM</t>
   </si>
   <si>
-    <t>Smart QLED Tivi 4K Samsung 65Q60DA 65 inch QA65Q60DA QA65Q60D 65Q60D - Hàng chính hãng - Chỉ giao HCM</t>
-  </si>
-  <si>
-    <t>images/tv/product_278220734.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_278138258.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_278138206.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_278077419.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_278077327.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_278006178.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_277989480.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_277989405.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_277988926.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_277988890.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_277976029.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_277972475.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_277972387.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_277971948.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_277971781.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_277429931.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_276931435.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_276389560.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_276268195.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_276178085.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_275987600.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_275646608.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_275603347.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_275603123.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_275269812.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_275247634.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_275194363.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_275020992.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_275019168.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_274877090.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_274870710.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_274843323.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_253498992.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_248237801.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_246208809.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_197920267.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_118537278.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_73681047.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_49089541.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_2003079.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_277991140.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_277575279.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_277485884.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_276921311.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_276860956.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_276621107.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_276606293.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_276387015.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_276379164.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_276362981.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_276319244.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_276252722.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_276089188.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_276032905.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_275803796.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_275603494.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_275602893.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_275249107.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_275245456.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_275245427.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_275244717.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_275020293.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_274969952.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_274876803.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_274870404.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_274843351.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_274843293.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_263584620.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_253502839.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_248208320.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_207872108.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_197883135.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_189176771.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_178093791.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_178062046.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_178058676.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_176058957.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_92504473.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_90655703.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_72797571.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_277575237.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_276862301.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_276861683.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_276861471.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_276621654.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_276606018.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_276415813.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_276412014.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_275805126.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_275655645.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_275655333.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_275603326.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_275270303.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_275268806.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_275249046.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_275245028.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_275244939.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_275244561.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_274880735.jpg</t>
-  </si>
-  <si>
-    <t>images/tv/product_274870762.jpg</t>
+    <t>images/tv/278220734.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/278138258.png</t>
+  </si>
+  <si>
+    <t>images/tv/278077419.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/278077327.png</t>
+  </si>
+  <si>
+    <t>images/tv/278009387.png</t>
+  </si>
+  <si>
+    <t>images/tv/278006178.png</t>
+  </si>
+  <si>
+    <t>images/tv/277991140.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/277989480.png</t>
+  </si>
+  <si>
+    <t>images/tv/277989405.png</t>
+  </si>
+  <si>
+    <t>images/tv/277988926.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/277988890.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/277976029.png</t>
+  </si>
+  <si>
+    <t>images/tv/277972475.png</t>
+  </si>
+  <si>
+    <t>images/tv/277972387.png</t>
+  </si>
+  <si>
+    <t>images/tv/277971948.png</t>
+  </si>
+  <si>
+    <t>images/tv/277971781.png</t>
+  </si>
+  <si>
+    <t>images/tv/277429931.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/276931435.png</t>
+  </si>
+  <si>
+    <t>images/tv/276389560.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/276268195.png</t>
+  </si>
+  <si>
+    <t>images/tv/275987600.png</t>
+  </si>
+  <si>
+    <t>images/tv/275646608.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/275603347.png</t>
+  </si>
+  <si>
+    <t>images/tv/275603123.png</t>
+  </si>
+  <si>
+    <t>images/tv/275269812.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/275247634.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/275194363.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/275135940.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/275019168.png</t>
+  </si>
+  <si>
+    <t>images/tv/274877090.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/274870710.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/274843323.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/253498992.png</t>
+  </si>
+  <si>
+    <t>images/tv/248237801.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/246208809.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/204338709.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/197920267.png</t>
+  </si>
+  <si>
+    <t>images/tv/118537278.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/49089541.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/7532597.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/277485884.png</t>
+  </si>
+  <si>
+    <t>images/tv/276921311.png</t>
+  </si>
+  <si>
+    <t>images/tv/276860956.png</t>
+  </si>
+  <si>
+    <t>images/tv/276621107.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/276606293.png</t>
+  </si>
+  <si>
+    <t>images/tv/276606018.png</t>
+  </si>
+  <si>
+    <t>images/tv/276387015.png</t>
+  </si>
+  <si>
+    <t>images/tv/276379164.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/276362981.png</t>
+  </si>
+  <si>
+    <t>images/tv/276089188.png</t>
+  </si>
+  <si>
+    <t>images/tv/276032905.png</t>
+  </si>
+  <si>
+    <t>images/tv/275803796.png</t>
+  </si>
+  <si>
+    <t>images/tv/275603494.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/275602893.png</t>
+  </si>
+  <si>
+    <t>images/tv/275245456.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/275245427.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/275244717.png</t>
+  </si>
+  <si>
+    <t>images/tv/275136307.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/275020293.png</t>
+  </si>
+  <si>
+    <t>images/tv/274969952.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/274870404.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/274843351.png</t>
+  </si>
+  <si>
+    <t>images/tv/263584620.png</t>
+  </si>
+  <si>
+    <t>images/tv/253502839.png</t>
+  </si>
+  <si>
+    <t>images/tv/249033305.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/248208320.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/207872108.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/204337932.png</t>
+  </si>
+  <si>
+    <t>images/tv/199171334.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/197883135.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/189176771.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/178093791.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/178062046.png</t>
+  </si>
+  <si>
+    <t>images/tv/178058676.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/176058957.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/92504473.png</t>
+  </si>
+  <si>
+    <t>images/tv/90655703.png</t>
+  </si>
+  <si>
+    <t>images/tv/73681047.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/72797571.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/2003079.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/276862301.png</t>
+  </si>
+  <si>
+    <t>images/tv/276861683.png</t>
+  </si>
+  <si>
+    <t>images/tv/276861471.png</t>
+  </si>
+  <si>
+    <t>images/tv/276621654.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/276606449.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/276415813.png</t>
+  </si>
+  <si>
+    <t>images/tv/276412014.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/276412010.jpg</t>
+  </si>
+  <si>
+    <t>images/tv/275655645.png</t>
+  </si>
+  <si>
+    <t>images/tv/275603326.png</t>
+  </si>
+  <si>
+    <t>images/tv/275602959.png</t>
+  </si>
+  <si>
+    <t>images/tv/275270303.png</t>
+  </si>
+  <si>
+    <t>images/tv/275268806.png</t>
+  </si>
+  <si>
+    <t>images/tv/275249046.png</t>
+  </si>
+  <si>
+    <t>images/tv/275245028.png</t>
+  </si>
+  <si>
+    <t>images/tv/275244939.png</t>
+  </si>
+  <si>
+    <t>images/tv/275244561.png</t>
+  </si>
+  <si>
+    <t>images/tv/275020992.png</t>
+  </si>
+  <si>
+    <t>images/tv/274887957.jpeg</t>
+  </si>
+  <si>
+    <t>images/tv/274880735.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/cd/71/4c/613a7ab05ab87bd2beb2f6d8feba71c1.jpg</t>
@@ -637,18 +637,21 @@
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/88/02/35/75310379554d351e16e9d42a96a0c4b8.png</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/38/79/88/0615d25b9ef28187e79ed24d0a617261.png</t>
-  </si>
-  <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/71/a4/a2/a5a9535dfc1bb59ab94b18f82bf0542d.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/e2/bf/4d/3b670d06064a1c87308270597a896f63.png</t>
   </si>
   <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/29/d3/a1/1e0653cf28eacbbaf454a216f82ae639.png</t>
+  </si>
+  <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/9e/be/7b/4b7469975ea9fb114d4aa8e7299c1c91.png</t>
   </si>
   <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/38/9f/db/ce70ad70513f8bead0b0da6ac225dbdd.jpg</t>
+  </si>
+  <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/66/72/04/c4e09fc7d7a6756957a49dfa1609d603.png</t>
   </si>
   <si>
@@ -688,22 +691,19 @@
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/f7/15/1c/cc0f67740bb4cff6562a6449dd61b5d5.png</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/media/catalog/producttmp/b3/77/2f/f7cc58e0f10ca04e8eb3233c208dd201.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/56/61/15/4e3161ec96968711a7a2a53d715ef23c.png</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/9b/e8/27/66cb7955c4ab3979c1f5d045e4e65641.png</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/53/52/ef/2c76b7a3a254c8e3edbe77ed4754af47.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/62/4b/70/83b4b79382bfef3c12bf4ed0ee549d54.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/a2/3f/37/b52e32322ac61fbe924be404d27ee2ce.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/7f/e1/14/1829eda7b65331f50ed7c8db1286aed4.png</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ef/61/a7/dc88054785afd12cbe90b038ce3ba4c6.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/54/d7/26/f86991076067dddeedece6ced22c3387.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/22/3e/b5/d97a89a04f677889c01674698fbf84b7.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/7a/16/23/7e466d1881b4008cb0e7cb9029652103.jpg</t>
@@ -712,7 +712,7 @@
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/52/8f/c0/e3335770ddd84742ca070f21bb80e167.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/1c/b7/85/44c4324541b028b753de8f78470aebbf.jpg</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/c4/b6/8f/de4fd8f5e7ef42a0822302b6b55b65c9.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/1e/c6/be/07b4a9f3e3bea1083ee2460881980976.jpg</t>
@@ -736,144 +736,141 @@
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/9f/64/f0/cb0406e3596f74ca73fc7c598fafec19.jpg</t>
   </si>
   <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/36/98/c3/2b57856f438eaa67d23de3c661cfdf45.jpg</t>
+  </si>
+  <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/d4/49/5a/30784a1e7c4d001f5c0c1dbb90167c00.png</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/fc/86/7e/37cdfcdf2f09100d63209ad62f78c6f0.jpg</t>
   </si>
   <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/75/cb/ff/429dcb6a786f0e9621be8e1206a8807b.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/37/f3/c1/06d87c0a02a0ab8390ee4b8267629be7.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/39/84/2d/34feaa2e1294a2253a99d330c2a71471.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/f4/35/df/eb2f34cc42060403c6421cd9fa21b673.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ed/42/fe/f34df7a15b672307e4491d8c85850e56.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/73/85/ab/258a2d31519a44e1c121c48fc728a7a8.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/83/c0/fe/71448b7a57557488f7a26730f09874e5.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/55/38/ba/b2ceea4aa0042e55711d65984ee9858a.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/aa/0b/43/93e8e431ed5c8f81095820c93ffa8e14.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/02/8f/40/c00a33456f72ad8375c1434891f76d3e.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/c6/98/55/7c6f16897841bbcef9487c1ae5560d1f.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/4d/5b/fe/a28a95b3393fd24c82bac1ad4df0e57e.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/6f/c3/29/ef77572e76d3c428c15aa0e923219b51.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/55/b9/51/69e6609fb15d44a28920455af59caa97.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/83/5e/c4/282401d53267adc2e9d37a086e5f31b1.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/a4/8d/f3/16f4c9b6672c9df8c806adedd3777ee2.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/cf/b3/8e/8834b846ca6c8c7d3b18a56efb85dd36.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/43/41/68/9cb9c7ad797d34b500d4faf50182170e.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/86/0b/72/68a2b4e7362df63cfc665210deaf3bae.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/82/8c/10/e3da8cf6afee0bcacd7ffb9c9a1f5648.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/1e/c6/be/b00a473274799a87fe8d383de43b03e1.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/08/95/69/6637c09a7c903698f1aa03f3b44b254d.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/c0/71/a7/45ff5a80084cc62dd46405a3318544d1.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ab/61/cb/45aa1628e424fcf9123062b1ee46616e.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/28/58/4a/ef1296df12af85b0ab72d691ecf5beab.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e9/f2/74/fc175e62b0ed7691397f102a74616f05.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/7c/56/f7/4319e097f49a43b85ce82b89819709f7.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/91/63/2f/e86442ba3a9fc738f39d0662a848e375.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/cc/0c/46/13fb2f32f7482abd727e75f3ef27cad1.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e3/1a/68/5c419e966185bdbdcf4214a38d5b70c7.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/83/8b/50/c75ef7ca508c22061b1cfbee3ba0575d.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/5d/b6/75/4a4ce9c9399e4ee1b01eee6eb590bc71.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/cc/80/27/106c5de13d425558fdbd1aebd5ec3719.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/7c/91/00/9c8cf822c9b992030600c0ea09011ea9.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/c8/4e/4c/fc286cd915b6085bfe8794b0035151aa.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/56/5d/a2/2a24cf8c4ca937b9a306221b36c8068a.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/86/63/f0/e9d5694098f4728a55964356a0397b5a.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/d3/79/3a/21d5daa2cdef04a2e271521ad6a71286.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/53/e2/54/c3696b513c951625a3999f6af1cc2fdc.png</t>
+  </si>
+  <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/66/a6/15/2e2971e88e43f345f8154dbd2234176a.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/75/cb/ff/429dcb6a786f0e9621be8e1206a8807b.jpg</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/30/3c/58/eb7826f4f1788aa21dff5c3debbf3ad9.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/64/b9/dd/94550d391168fa26475a53ff02aaf6e0.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/38/9f/db/ce70ad70513f8bead0b0da6ac225dbdd.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/97/b1/e5/977a6bbad5b934a6ae809f5436c1e950.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/39/84/2d/34feaa2e1294a2253a99d330c2a71471.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/f4/35/df/eb2f34cc42060403c6421cd9fa21b673.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ed/42/fe/f34df7a15b672307e4491d8c85850e56.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/73/85/ab/258a2d31519a44e1c121c48fc728a7a8.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/83/c0/fe/71448b7a57557488f7a26730f09874e5.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/aa/0b/43/93e8e431ed5c8f81095820c93ffa8e14.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/44/a0/fc/9f0f8b8187b95320bdf3650cca22713b.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/c6/98/55/7c6f16897841bbcef9487c1ae5560d1f.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/43/37/9d/fa70ce097b81ac0360df39199b8eb951.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/1f/bc/77/22d6c668b8e7185c82939fd59f112cf9.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/4d/5b/fe/a28a95b3393fd24c82bac1ad4df0e57e.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/6f/c3/29/ef77572e76d3c428c15aa0e923219b51.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/55/b9/51/69e6609fb15d44a28920455af59caa97.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ae/da/43/febf2db6ac490b9b997ceb860a1635e0.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/0f/b2/1c/4c332a6e22b0211485ed05cb3471c9d9.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/80/59/4d/a27a2b6e42f714f6f3921dd8fed57433.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ee/5c/6d/f1912f686f179ec7c244555083d96c2c.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/43/41/68/9cb9c7ad797d34b500d4faf50182170e.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/86/0b/72/68a2b4e7362df63cfc665210deaf3bae.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/1e/c6/be/b00a473274799a87fe8d383de43b03e1.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/08/95/69/6637c09a7c903698f1aa03f3b44b254d.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/c2/a8/77/a93f5e365daae2972ac058b4338fc6b4.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/c0/71/a7/45ff5a80084cc62dd46405a3318544d1.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ab/61/cb/45aa1628e424fcf9123062b1ee46616e.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/ce/bf/01/1ab259b3117e14b830a0d7a9e93303d4.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/28/58/4a/ef1296df12af85b0ab72d691ecf5beab.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e9/f2/74/fc175e62b0ed7691397f102a74616f05.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/91/63/2f/e86442ba3a9fc738f39d0662a848e375.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/cc/0c/46/13fb2f32f7482abd727e75f3ef27cad1.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/5d/b6/75/4a4ce9c9399e4ee1b01eee6eb590bc71.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/cc/80/27/106c5de13d425558fdbd1aebd5ec3719.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/7c/91/00/9c8cf822c9b992030600c0ea09011ea9.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/c8/4e/4c/fc286cd915b6085bfe8794b0035151aa.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/56/5d/a2/2a24cf8c4ca937b9a306221b36c8068a.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/86/63/f0/e9d5694098f4728a55964356a0397b5a.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/d3/79/3a/21d5daa2cdef04a2e271521ad6a71286.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/53/e2/54/c3696b513c951625a3999f6af1cc2fdc.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/30/3c/58/eb7826f4f1788aa21dff5c3debbf3ad9.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/e2/9c/bb/50eabadb5ef6b4f01595fccda6f3d7b6.png</t>
-  </si>
-  <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/97/c7/f8/32b1d5d0cbd3e338720852f5f8d72bc4.png</t>
   </si>
   <si>
@@ -886,28 +883,28 @@
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/5c/cb/64/bb4bdb0f4ed531dfde10b5b26f93094e.jpg</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/55/38/ba/b2ceea4aa0042e55711d65984ee9858a.png</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/1f/cf/24/bc75ea5e78c5f89c3c2857e2114981b8.jpg</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/0b/b1/3e/70482294f07122f066828a1872cc0a91.png</t>
   </si>
   <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/15/ce/d5/32d3ba86b3954ec7d070dc3b2e999677.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/95/90/bd/1152f0efb91c9b24b488681791a7d9c5.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/eb/09/86/1da747b3b509f317dfbd68d4f8f57259.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/d6/bf/85/2830ab133338d9d358d6b12f18aabc11.png</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/f8/0a/a7/98f2a7f46efed4f68d058f84a31d0d1b.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/eb/09/86/1d240c4dae4d7e6c1ab741698c42dea6.png</t>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/2e/71/fd/e5032b291ee6188511d24f27f06dd59b.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/8b/ff/52/568c4844ea8753542ef715882f2d2a68.jpg</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/0f/f0/c6/ffebb4b6b9ee57a7143a06f76eba5a11.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/d5/4b/bc/de9b4866f843a3ad15d4c4b91b029947.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/8e/33/89/45991eb0de9e80d50e7ce19163267855.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/4a/1a/a3/3e317abfe9fff5816863c728c23731bc.png</t>
   </si>
   <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/21/3f/0c/73fff16384357e8e7e0b3a596f5548ed.png</t>
@@ -925,10 +922,13 @@
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/9d/aa/80/158d513196e5a390a5703ce07cb88c0c.png</t>
   </si>
   <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/63/3d/fc/cf3b98970277243945b78eeb13c08a0c.png</t>
+  </si>
+  <si>
+    <t>https://salt.tikicdn.com/cache/280x280/ts/product/3e/59/dc/0242c78ca805349696b857f2d6e4ecc7.jpeg</t>
+  </si>
+  <si>
     <t>https://salt.tikicdn.com/cache/280x280/ts/product/38/37/78/c224aef47fd8219cbb9bbfe1a23fb5f8.jpg</t>
-  </si>
-  <si>
-    <t>https://salt.tikicdn.com/cache/280x280/ts/product/37/e1/02/5f59a69630d73f55482c6c1f51d7f0f9.jpg</t>
   </si>
   <si>
     <t>Điện Tử - Điện Lạnh</t>
@@ -1358,7 +1358,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>278138206</v>
+        <v>278077419</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -1375,7 +1375,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>278077419</v>
+        <v>278077327</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
@@ -1392,7 +1392,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>278077327</v>
+        <v>278009387</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
@@ -1426,7 +1426,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>277989480</v>
+        <v>277991140</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
@@ -1443,7 +1443,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>277989405</v>
+        <v>277989480</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -1460,7 +1460,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>277988926</v>
+        <v>277989405</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -1477,7 +1477,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>277988890</v>
+        <v>277988926</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
@@ -1494,7 +1494,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>277976029</v>
+        <v>277988890</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
@@ -1511,7 +1511,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>277972475</v>
+        <v>277976029</v>
       </c>
       <c r="B13" t="s">
         <v>16</v>
@@ -1528,7 +1528,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>277972387</v>
+        <v>277972475</v>
       </c>
       <c r="B14" t="s">
         <v>17</v>
@@ -1545,7 +1545,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>277971948</v>
+        <v>277972387</v>
       </c>
       <c r="B15" t="s">
         <v>18</v>
@@ -1562,7 +1562,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>277971781</v>
+        <v>277971948</v>
       </c>
       <c r="B16" t="s">
         <v>19</v>
@@ -1579,7 +1579,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>277429931</v>
+        <v>277971781</v>
       </c>
       <c r="B17" t="s">
         <v>20</v>
@@ -1596,7 +1596,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>276931435</v>
+        <v>277429931</v>
       </c>
       <c r="B18" t="s">
         <v>21</v>
@@ -1613,7 +1613,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>276389560</v>
+        <v>276931435</v>
       </c>
       <c r="B19" t="s">
         <v>22</v>
@@ -1630,7 +1630,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>276268195</v>
+        <v>276389560</v>
       </c>
       <c r="B20" t="s">
         <v>23</v>
@@ -1647,7 +1647,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>276178085</v>
+        <v>276268195</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
@@ -1783,7 +1783,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>275020992</v>
+        <v>275135940</v>
       </c>
       <c r="B29" t="s">
         <v>32</v>
@@ -1919,7 +1919,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>197920267</v>
+        <v>204338709</v>
       </c>
       <c r="B37" t="s">
         <v>40</v>
@@ -1936,7 +1936,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>118537278</v>
+        <v>197920267</v>
       </c>
       <c r="B38" t="s">
         <v>41</v>
@@ -1953,7 +1953,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>73681047</v>
+        <v>118537278</v>
       </c>
       <c r="B39" t="s">
         <v>42</v>
@@ -1987,7 +1987,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>2003079</v>
+        <v>7532597</v>
       </c>
       <c r="B41" t="s">
         <v>44</v>
@@ -2004,7 +2004,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>277991140</v>
+        <v>277485884</v>
       </c>
       <c r="B42" t="s">
         <v>45</v>
@@ -2021,7 +2021,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>277575279</v>
+        <v>276921311</v>
       </c>
       <c r="B43" t="s">
         <v>46</v>
@@ -2038,7 +2038,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44">
-        <v>277485884</v>
+        <v>276860956</v>
       </c>
       <c r="B44" t="s">
         <v>47</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45">
-        <v>276921311</v>
+        <v>276621107</v>
       </c>
       <c r="B45" t="s">
         <v>48</v>
@@ -2072,7 +2072,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46">
-        <v>276860956</v>
+        <v>276606293</v>
       </c>
       <c r="B46" t="s">
         <v>49</v>
@@ -2089,7 +2089,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47">
-        <v>276621107</v>
+        <v>276606018</v>
       </c>
       <c r="B47" t="s">
         <v>50</v>
@@ -2106,7 +2106,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48">
-        <v>276606293</v>
+        <v>276387015</v>
       </c>
       <c r="B48" t="s">
         <v>51</v>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49">
-        <v>276387015</v>
+        <v>276379164</v>
       </c>
       <c r="B49" t="s">
         <v>52</v>
@@ -2140,7 +2140,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50">
-        <v>276379164</v>
+        <v>276362981</v>
       </c>
       <c r="B50" t="s">
         <v>53</v>
@@ -2157,7 +2157,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51">
-        <v>276362981</v>
+        <v>276089188</v>
       </c>
       <c r="B51" t="s">
         <v>54</v>
@@ -2174,7 +2174,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52">
-        <v>276319244</v>
+        <v>276032905</v>
       </c>
       <c r="B52" t="s">
         <v>55</v>
@@ -2191,7 +2191,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53">
-        <v>276252722</v>
+        <v>275803796</v>
       </c>
       <c r="B53" t="s">
         <v>56</v>
@@ -2208,7 +2208,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54">
-        <v>276089188</v>
+        <v>275603494</v>
       </c>
       <c r="B54" t="s">
         <v>57</v>
@@ -2225,7 +2225,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55">
-        <v>276032905</v>
+        <v>275602893</v>
       </c>
       <c r="B55" t="s">
         <v>58</v>
@@ -2242,7 +2242,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56">
-        <v>275803796</v>
+        <v>275245456</v>
       </c>
       <c r="B56" t="s">
         <v>59</v>
@@ -2259,7 +2259,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57">
-        <v>275603494</v>
+        <v>275245427</v>
       </c>
       <c r="B57" t="s">
         <v>60</v>
@@ -2276,7 +2276,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58">
-        <v>275602893</v>
+        <v>275244717</v>
       </c>
       <c r="B58" t="s">
         <v>61</v>
@@ -2293,7 +2293,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59">
-        <v>275249107</v>
+        <v>275136307</v>
       </c>
       <c r="B59" t="s">
         <v>62</v>
@@ -2310,7 +2310,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60">
-        <v>275245456</v>
+        <v>275020293</v>
       </c>
       <c r="B60" t="s">
         <v>63</v>
@@ -2327,7 +2327,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61">
-        <v>275245427</v>
+        <v>274969952</v>
       </c>
       <c r="B61" t="s">
         <v>64</v>
@@ -2344,7 +2344,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62">
-        <v>275244717</v>
+        <v>274870404</v>
       </c>
       <c r="B62" t="s">
         <v>65</v>
@@ -2361,7 +2361,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63">
-        <v>275020293</v>
+        <v>274843351</v>
       </c>
       <c r="B63" t="s">
         <v>66</v>
@@ -2378,7 +2378,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64">
-        <v>274969952</v>
+        <v>263584620</v>
       </c>
       <c r="B64" t="s">
         <v>67</v>
@@ -2395,7 +2395,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65">
-        <v>274876803</v>
+        <v>253502839</v>
       </c>
       <c r="B65" t="s">
         <v>68</v>
@@ -2412,7 +2412,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66">
-        <v>274870404</v>
+        <v>249033305</v>
       </c>
       <c r="B66" t="s">
         <v>69</v>
@@ -2429,7 +2429,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67">
-        <v>274843351</v>
+        <v>248208320</v>
       </c>
       <c r="B67" t="s">
         <v>70</v>
@@ -2446,7 +2446,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68">
-        <v>274843293</v>
+        <v>207872108</v>
       </c>
       <c r="B68" t="s">
         <v>71</v>
@@ -2463,7 +2463,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69">
-        <v>263584620</v>
+        <v>204337932</v>
       </c>
       <c r="B69" t="s">
         <v>72</v>
@@ -2480,7 +2480,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70">
-        <v>253502839</v>
+        <v>199171334</v>
       </c>
       <c r="B70" t="s">
         <v>73</v>
@@ -2497,7 +2497,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71">
-        <v>248208320</v>
+        <v>197883135</v>
       </c>
       <c r="B71" t="s">
         <v>74</v>
@@ -2514,7 +2514,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72">
-        <v>207872108</v>
+        <v>189176771</v>
       </c>
       <c r="B72" t="s">
         <v>75</v>
@@ -2531,7 +2531,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73">
-        <v>197883135</v>
+        <v>178093791</v>
       </c>
       <c r="B73" t="s">
         <v>76</v>
@@ -2548,7 +2548,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74">
-        <v>189176771</v>
+        <v>178062046</v>
       </c>
       <c r="B74" t="s">
         <v>77</v>
@@ -2565,7 +2565,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75">
-        <v>178093791</v>
+        <v>178058676</v>
       </c>
       <c r="B75" t="s">
         <v>78</v>
@@ -2582,7 +2582,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76">
-        <v>178062046</v>
+        <v>176058957</v>
       </c>
       <c r="B76" t="s">
         <v>79</v>
@@ -2599,7 +2599,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77">
-        <v>178058676</v>
+        <v>92504473</v>
       </c>
       <c r="B77" t="s">
         <v>80</v>
@@ -2616,7 +2616,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78">
-        <v>176058957</v>
+        <v>90655703</v>
       </c>
       <c r="B78" t="s">
         <v>81</v>
@@ -2633,7 +2633,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79">
-        <v>92504473</v>
+        <v>73681047</v>
       </c>
       <c r="B79" t="s">
         <v>82</v>
@@ -2650,7 +2650,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80">
-        <v>90655703</v>
+        <v>72797571</v>
       </c>
       <c r="B80" t="s">
         <v>83</v>
@@ -2667,7 +2667,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81">
-        <v>72797571</v>
+        <v>2003079</v>
       </c>
       <c r="B81" t="s">
         <v>84</v>
@@ -2684,7 +2684,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82">
-        <v>277575237</v>
+        <v>276862301</v>
       </c>
       <c r="B82" t="s">
         <v>85</v>
@@ -2701,7 +2701,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83">
-        <v>276862301</v>
+        <v>276861683</v>
       </c>
       <c r="B83" t="s">
         <v>86</v>
@@ -2718,7 +2718,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84">
-        <v>276861683</v>
+        <v>276861471</v>
       </c>
       <c r="B84" t="s">
         <v>87</v>
@@ -2735,7 +2735,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85">
-        <v>276861471</v>
+        <v>276621654</v>
       </c>
       <c r="B85" t="s">
         <v>88</v>
@@ -2752,7 +2752,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86">
-        <v>276621654</v>
+        <v>276606449</v>
       </c>
       <c r="B86" t="s">
         <v>89</v>
@@ -2769,7 +2769,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87">
-        <v>276606018</v>
+        <v>276415813</v>
       </c>
       <c r="B87" t="s">
         <v>90</v>
@@ -2786,7 +2786,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88">
-        <v>276415813</v>
+        <v>276412014</v>
       </c>
       <c r="B88" t="s">
         <v>91</v>
@@ -2803,7 +2803,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89">
-        <v>276412014</v>
+        <v>276412010</v>
       </c>
       <c r="B89" t="s">
         <v>92</v>
@@ -2820,7 +2820,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90">
-        <v>275805126</v>
+        <v>275655645</v>
       </c>
       <c r="B90" t="s">
         <v>93</v>
@@ -2837,7 +2837,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91">
-        <v>275655645</v>
+        <v>275603326</v>
       </c>
       <c r="B91" t="s">
         <v>94</v>
@@ -2854,7 +2854,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92">
-        <v>275655333</v>
+        <v>275602959</v>
       </c>
       <c r="B92" t="s">
         <v>95</v>
@@ -2871,7 +2871,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93">
-        <v>275603326</v>
+        <v>275270303</v>
       </c>
       <c r="B93" t="s">
         <v>96</v>
@@ -2888,7 +2888,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94">
-        <v>275270303</v>
+        <v>275268806</v>
       </c>
       <c r="B94" t="s">
         <v>97</v>
@@ -2905,7 +2905,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95">
-        <v>275268806</v>
+        <v>275249046</v>
       </c>
       <c r="B95" t="s">
         <v>98</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96">
-        <v>275249046</v>
+        <v>275245028</v>
       </c>
       <c r="B96" t="s">
         <v>99</v>
@@ -2939,7 +2939,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97">
-        <v>275245028</v>
+        <v>275244939</v>
       </c>
       <c r="B97" t="s">
         <v>100</v>
@@ -2956,7 +2956,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98">
-        <v>275244939</v>
+        <v>275244561</v>
       </c>
       <c r="B98" t="s">
         <v>101</v>
@@ -2973,7 +2973,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99">
-        <v>275244561</v>
+        <v>275020992</v>
       </c>
       <c r="B99" t="s">
         <v>102</v>
@@ -2990,7 +2990,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100">
-        <v>274880735</v>
+        <v>274887957</v>
       </c>
       <c r="B100" t="s">
         <v>103</v>
@@ -3007,7 +3007,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101">
-        <v>274870762</v>
+        <v>274880735</v>
       </c>
       <c r="B101" t="s">
         <v>104</v>
